--- a/etf_holdings/2026-10-06_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00993A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:01</t>
+          <t>2026-10-06 01:25:06</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:01</t>
+          <t>2026-10-06 01:25:06</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:01</t>
+          <t>2026-10-06 01:25:06</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:01</t>
+          <t>2026-10-06 01:25:06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:01</t>
+          <t>2026-10-06 01:25:06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:01</t>
+          <t>2026-10-06 01:25:06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:01</t>
+          <t>2026-10-06 01:25:06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:01</t>
+          <t>2026-10-06 01:25:06</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:01</t>
+          <t>2026-10-06 01:25:06</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:01</t>
+          <t>2026-10-06 01:25:06</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:01</t>
+          <t>2026-10-06 01:25:06</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:01</t>
+          <t>2026-10-06 01:25:06</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:01</t>
+          <t>2026-10-06 01:25:06</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:01</t>
+          <t>2026-10-06 01:25:06</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:01</t>
+          <t>2026-10-06 01:25:06</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:03</t>
+          <t>2026-10-06 01:25:07</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:03</t>
+          <t>2026-10-06 01:25:07</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:03</t>
+          <t>2026-10-06 01:25:07</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:03</t>
+          <t>2026-10-06 01:25:07</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:03</t>
+          <t>2026-10-06 01:25:07</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:03</t>
+          <t>2026-10-06 01:25:07</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:03</t>
+          <t>2026-10-06 01:25:07</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:03</t>
+          <t>2026-10-06 01:25:07</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:03</t>
+          <t>2026-10-06 01:25:07</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:03</t>
+          <t>2026-10-06 01:25:07</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:03</t>
+          <t>2026-10-06 01:25:07</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:03</t>
+          <t>2026-10-06 01:25:07</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:03</t>
+          <t>2026-10-06 01:25:07</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:03</t>
+          <t>2026-10-06 01:25:07</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:03</t>
+          <t>2026-10-06 01:25:07</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:04</t>
+          <t>2026-10-06 01:25:09</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:04</t>
+          <t>2026-10-06 01:25:09</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:04</t>
+          <t>2026-10-06 01:25:09</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:04</t>
+          <t>2026-10-06 01:25:09</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:04</t>
+          <t>2026-10-06 01:25:09</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:04</t>
+          <t>2026-10-06 01:25:09</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:04</t>
+          <t>2026-10-06 01:25:09</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:04</t>
+          <t>2026-10-06 01:25:09</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:04</t>
+          <t>2026-10-06 01:25:09</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:04</t>
+          <t>2026-10-06 01:25:09</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:04</t>
+          <t>2026-10-06 01:25:09</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:04</t>
+          <t>2026-10-06 01:25:09</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:04</t>
+          <t>2026-10-06 01:25:09</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:04</t>
+          <t>2026-10-06 01:25:09</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:04</t>
+          <t>2026-10-06 01:25:09</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:05</t>
+          <t>2026-10-06 01:25:10</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:05</t>
+          <t>2026-10-06 01:25:10</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:05</t>
+          <t>2026-10-06 01:25:10</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:05</t>
+          <t>2026-10-06 01:25:10</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:05</t>
+          <t>2026-10-06 01:25:10</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:05</t>
+          <t>2026-10-06 01:25:10</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">

--- a/etf_holdings/2026-10-06_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00993A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:06</t>
+          <t>2026-10-06 02:28:36</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:06</t>
+          <t>2026-10-06 02:28:36</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:06</t>
+          <t>2026-10-06 02:28:36</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:06</t>
+          <t>2026-10-06 02:28:36</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:06</t>
+          <t>2026-10-06 02:28:36</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:06</t>
+          <t>2026-10-06 02:28:36</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:06</t>
+          <t>2026-10-06 02:28:36</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:06</t>
+          <t>2026-10-06 02:28:36</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:06</t>
+          <t>2026-10-06 02:28:36</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:06</t>
+          <t>2026-10-06 02:28:36</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:06</t>
+          <t>2026-10-06 02:28:36</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:06</t>
+          <t>2026-10-06 02:28:36</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:06</t>
+          <t>2026-10-06 02:28:36</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:06</t>
+          <t>2026-10-06 02:28:36</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:06</t>
+          <t>2026-10-06 02:28:36</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:07</t>
+          <t>2026-10-06 02:28:37</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:07</t>
+          <t>2026-10-06 02:28:37</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:07</t>
+          <t>2026-10-06 02:28:37</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:07</t>
+          <t>2026-10-06 02:28:37</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:07</t>
+          <t>2026-10-06 02:28:37</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:07</t>
+          <t>2026-10-06 02:28:37</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:07</t>
+          <t>2026-10-06 02:28:37</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:07</t>
+          <t>2026-10-06 02:28:37</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:07</t>
+          <t>2026-10-06 02:28:37</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:07</t>
+          <t>2026-10-06 02:28:37</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:07</t>
+          <t>2026-10-06 02:28:37</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:07</t>
+          <t>2026-10-06 02:28:37</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:07</t>
+          <t>2026-10-06 02:28:37</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:07</t>
+          <t>2026-10-06 02:28:37</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:07</t>
+          <t>2026-10-06 02:28:37</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:09</t>
+          <t>2026-10-06 02:28:38</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:09</t>
+          <t>2026-10-06 02:28:38</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:09</t>
+          <t>2026-10-06 02:28:38</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:09</t>
+          <t>2026-10-06 02:28:38</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:09</t>
+          <t>2026-10-06 02:28:38</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:09</t>
+          <t>2026-10-06 02:28:38</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:09</t>
+          <t>2026-10-06 02:28:38</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:09</t>
+          <t>2026-10-06 02:28:38</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:09</t>
+          <t>2026-10-06 02:28:38</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:09</t>
+          <t>2026-10-06 02:28:38</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:09</t>
+          <t>2026-10-06 02:28:38</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:09</t>
+          <t>2026-10-06 02:28:38</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:09</t>
+          <t>2026-10-06 02:28:38</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:09</t>
+          <t>2026-10-06 02:28:38</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:09</t>
+          <t>2026-10-06 02:28:38</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:10</t>
+          <t>2026-10-06 02:28:40</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:10</t>
+          <t>2026-10-06 02:28:40</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:10</t>
+          <t>2026-10-06 02:28:40</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:10</t>
+          <t>2026-10-06 02:28:40</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:10</t>
+          <t>2026-10-06 02:28:40</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:10</t>
+          <t>2026-10-06 02:28:40</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">

--- a/etf_holdings/2026-10-06_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00993A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:36</t>
+          <t>2026-10-06 19:17:43</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+3%2575</t>
+          <t>+0.39%2585</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+3%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2575</v>
+        <v>2585</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.51%349,000</t>
+          <t>8.34%349,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.51%</t>
+          <t>8.34%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:36</t>
+          <t>2026-10-06 19:17:43</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -565,38 +565,38 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+4.34%5165</t>
+          <t>-1.13%1310</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+4.34%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5165</v>
+        <v>1310</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.32%131,000</t>
+          <t>6.52%531,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.32%</t>
+          <t>6.52%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>131000</v>
+        <v>531000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.27%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:36</t>
+          <t>2026-10-06 19:17:43</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,38 +626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+1.53%1325</t>
+          <t>-4.74%4920</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+1.53%</t>
+          <t>-4.74%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1325</v>
+        <v>4920</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.25%531,000</t>
+          <t>6.27%131,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.25%</t>
+          <t>6.27%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>531000</v>
+        <v>131000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:36</t>
+          <t>2026-10-06 19:17:43</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+4.22%3585</t>
+          <t>+2.79%3685</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+4.22%</t>
+          <t>+2.79%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3585</v>
+        <v>3685</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.74%169,000</t>
+          <t>5.62%169,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.74%</t>
+          <t>5.62%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:36</t>
+          <t>2026-10-06 19:17:43</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,38 +748,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+8.86%8600</t>
+          <t>+5.18%5995</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+8.86%</t>
+          <t>+5.18%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>8600</v>
+        <v>5995</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.05%66,000</t>
+          <t>5.34%101,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.05%</t>
+          <t>5.34%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>66000</v>
+        <v>101000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:36</t>
+          <t>2026-10-06 19:17:43</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+9.93%5700</t>
+          <t>-2.62%8375</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+9.93%</t>
+          <t>-2.62%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>5700</v>
+        <v>8375</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.86%101,000</t>
+          <t>5.26%66,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.86%</t>
+          <t>5.26%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>101000</v>
+        <v>66000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.46%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:36</t>
+          <t>2026-10-06 19:17:43</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+4.29%1095</t>
+          <t>-2.28%1070</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+4.29%</t>
+          <t>-2.28%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1095</v>
+        <v>1070</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.30%440,000</t>
+          <t>4.47%440,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>4.47%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:36</t>
+          <t>2026-10-06 19:17:43</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+3.95%5520</t>
+          <t>+2.72%5670</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+3.95%</t>
+          <t>+2.72%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5520</v>
+        <v>5670</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.99%82,000</t>
+          <t>4.20%82,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.99%</t>
+          <t>4.20%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:36</t>
+          <t>2026-10-06 19:17:43</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+3.12%2150</t>
+          <t>+6.51%2290</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+3.12%</t>
+          <t>+6.51%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2150</v>
+        <v>2290</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.99%195,191</t>
+          <t>3.89%195,191</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.99%</t>
+          <t>3.89%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:36</t>
+          <t>2026-10-06 19:17:43</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+3.61%19520</t>
+          <t>-2.74%18985</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+3.61%</t>
+          <t>-2.74%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>19520</v>
+        <v>18985</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.80%20,600</t>
+          <t>3.73%20,600</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.80%</t>
+          <t>3.73%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:36</t>
+          <t>2026-10-06 19:17:43</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+2.4%1495</t>
+          <t>+0.67%1505</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+2.4%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1495</v>
+        <v>1505</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.49%254,000</t>
+          <t>3.52%254,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.49%</t>
+          <t>3.52%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:36</t>
+          <t>2026-10-06 19:17:43</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,25 +1180,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+0.76%530</t>
+          <t>-0.94%525</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+0.76%</t>
+          <t>-0.94%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.15%626,000</t>
+          <t>3.08%626,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.15%</t>
+          <t>3.08%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:36</t>
+          <t>2026-10-06 19:17:43</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,25 +1241,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-5.57%152.5</t>
+          <t>-3.28%147.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-5.57%</t>
+          <t>-3.28%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>152.5</v>
+        <v>147.5</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.03%1,938,000</t>
+          <t>2.74%1,938,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.03%</t>
+          <t>2.74%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:36</t>
+          <t>2026-10-06 19:17:43</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+5.96%7205</t>
+          <t>-1.73%7080</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+5.96%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>7205</v>
+        <v>7080</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.73%41,000</t>
+          <t>2.74%41,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.73%</t>
+          <t>2.74%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:36</t>
+          <t>2026-10-06 19:17:43</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+5.6%2075</t>
+          <t>-1.4%1755</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+5.6%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>2075</v>
+        <v>1755</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.37%129,000</t>
+          <t>2.62%159,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.37%</t>
+          <t>2.62%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>129000</v>
+        <v>159000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:37</t>
+          <t>2026-10-06 19:17:44</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>2059川湖</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+9.88%1780</t>
+          <t>-1.91%13100</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+9.88%</t>
+          <t>-1.91%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1780</v>
+        <v>13100</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.36%159,000</t>
+          <t>2.48%20,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.36%</t>
+          <t>2.48%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>159000</v>
+        <v>20000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:37</t>
+          <t>2026-10-06 19:17:44</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+9.96%13355</t>
+          <t>-1.2%2050</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+9.96%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>13355</v>
+        <v>2050</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.29%20,000</t>
+          <t>2.48%129,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.29%</t>
+          <t>2.48%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>20000</v>
+        <v>129000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:37</t>
+          <t>2026-10-06 19:17:44</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,25 +1546,25 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0%626</t>
+          <t>-0.16%625</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.26%388,000</t>
+          <t>2.25%388,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>2.25%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:37</t>
+          <t>2026-10-06 19:17:44</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,25 +1607,25 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+1.12%181</t>
+          <t>-1.93%177.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+1.12%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>181</v>
+        <v>177.5</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.12%1,214,000</t>
+          <t>2.04%1,214,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.12%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:37</t>
+          <t>2026-10-06 19:17:44</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-2.17%2485</t>
+          <t>+2.24%2050</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-2.17%</t>
+          <t>+2.24%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>2485</v>
+        <v>2050</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2.05%83,000</t>
+          <t>2.01%108,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>2.01%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>83000</v>
+        <v>108000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:37</t>
+          <t>2026-10-06 19:17:44</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>2455全新</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+6.37%2005</t>
+          <t>-6.44%567</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+6.37%</t>
+          <t>-6.44%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2005</v>
+        <v>567</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.99%108,000</t>
+          <t>1.96%348,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>1.96%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>108000</v>
+        <v>348000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:37</t>
+          <t>2026-10-06 19:17:44</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2455全新</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+4.48%606</t>
+          <t>-6.44%2325</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+4.48%</t>
+          <t>-6.44%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>606</v>
+        <v>2325</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.84%348,000</t>
+          <t>1.91%83,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.91%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>348000</v>
+        <v>83000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:37</t>
+          <t>2026-10-06 19:17:44</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,25 +1851,25 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+7%6730</t>
+          <t>+1.86%6855</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+7%</t>
+          <t>+1.86%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>6730</v>
+        <v>6855</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.56%26,000</t>
+          <t>1.62%26,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.62%</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:37</t>
+          <t>2026-10-06 19:17:44</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,25 +1912,25 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+10%286</t>
+          <t>+2.45%293</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+10%</t>
+          <t>+2.45%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.36%553,000</t>
+          <t>1.47%553,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:37</t>
+          <t>2026-10-06 19:17:44</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,25 +1973,25 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+2.67%576</t>
+          <t>-0.35%574</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+2.67%</t>
+          <t>-0.35%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.21%246,000</t>
+          <t>1.31%246,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.31%</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:37</t>
+          <t>2026-10-06 19:17:44</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,16 +2034,16 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+2.46%1040</t>
+          <t>-0.96%1030</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+2.46%</t>
+          <t>-0.96%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:37</t>
+          <t>2026-10-06 19:17:44</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,25 +2095,25 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+9.96%751</t>
+          <t>+4.79%787</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+9.96%</t>
+          <t>+4.79%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>751</v>
+        <v>787</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.65%105,000</t>
+          <t>0.73%105,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.65%</t>
+          <t>0.73%</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:37</t>
+          <t>2026-10-06 19:17:44</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,25 +2156,25 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+3.35%740</t>
+          <t>-0.27%738</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+3.35%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.63%90,000</t>
+          <t>0.62%90,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:37</t>
+          <t>2026-10-06 19:17:44</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,16 +2217,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+4.07%742</t>
+          <t>+0.27%744</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+4.07%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:37</t>
+          <t>2026-10-06 19:17:44</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,25 +2278,25 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+2.99%1550</t>
+          <t>-1.29%1530</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+2.99%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1550</v>
+        <v>1530</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.61%41,000</t>
+          <t>0.59%41,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>0.59%</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:38</t>
+          <t>2026-10-06 19:17:46</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,25 +2339,25 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-0.92%85.8</t>
+          <t>+0.93%86.6</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-0.92%</t>
+          <t>+0.93%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>85.8</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.57%699,000</t>
+          <t>0.56%699,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.56%</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:38</t>
+          <t>2026-10-06 19:17:46</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>6805富世達</t>
+          <t>3081聯亞</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+6.06%2450</t>
+          <t>-2.67%2920</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+6.06%</t>
+          <t>-2.67%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>2450</v>
+        <v>2920</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.51%22,000</t>
+          <t>0.53%19,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.53%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>22000</v>
+        <v>19000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:38</t>
+          <t>2026-10-06 19:17:46</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,25 +2456,25 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2412中華電</t>
+          <t>6805富世達</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-0.34%145.5</t>
+          <t>-1.43%2415</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-0.34%</t>
+          <t>-1.43%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>145.5</v>
+        <v>2415</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.50%357,000</t>
+          <t>0.50%22,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2483,11 +2483,11 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>357000</v>
+        <v>22000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:38</t>
+          <t>2026-10-06 19:17:46</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3081聯亞</t>
+          <t>2412中華電</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+2.56%3000</t>
+          <t>0%145.5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+2.56%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>3000</v>
+        <v>145.5</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.49%19,000</t>
+          <t>0.48%357,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>19000</v>
+        <v>357000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:38</t>
+          <t>2026-10-06 19:17:46</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,25 +2583,25 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-0.1%97</t>
+          <t>-1.24%95.8</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>-1.24%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>97</v>
+        <v>95.8</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.44%474,000</t>
+          <t>0.43%474,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:38</t>
+          <t>2026-10-06 19:17:46</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,25 +2644,25 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-1.26%469.5</t>
+          <t>-0.53%467</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-1.26%</t>
+          <t>-0.53%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>469.5</v>
+        <v>467</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.37%80,000</t>
+          <t>0.35%80,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:38</t>
+          <t>2026-10-06 19:17:46</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,25 +2700,25 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2606裕民</t>
+          <t>6505台塑化</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-2.11%74.3</t>
+          <t>+2.94%101.5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-2.11%</t>
+          <t>+2.94%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>74.3</v>
+        <v>101.5</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.35%498,000</t>
+          <t>0.35%378,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2727,11 +2727,11 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>498000</v>
+        <v>378000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:38</t>
+          <t>2026-10-06 19:17:46</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,25 +2761,25 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>6505台塑化</t>
+          <t>2606裕民</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-1.4%98.6</t>
+          <t>+1.35%75.3</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>+1.35%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>98.59999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.34%378,000</t>
+          <t>0.34%498,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2788,11 +2788,11 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>378000</v>
+        <v>498000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:38</t>
+          <t>2026-10-06 19:17:46</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2603長榮</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-2.29%234.5</t>
+          <t>+1.08%2350</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-2.29%</t>
+          <t>+1.08%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>234.5</v>
+        <v>2350</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.31%135,000</t>
+          <t>0.32%15,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>135000</v>
+        <v>15000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:38</t>
+          <t>2026-10-06 19:17:46</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,38 +2883,38 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>3406玉晶光</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+6.16%2325</t>
+          <t>-0.95%1045</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+6.16%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>2325</v>
+        <v>1045</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.30%15,000</t>
+          <t>0.32%33,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>15000</v>
+        <v>33000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:38</t>
+          <t>2026-10-06 19:17:46</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,38 +2944,38 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>3406玉晶光</t>
+          <t>2603長榮</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+9.78%1055</t>
+          <t>+0.85%236.5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+9.78%</t>
+          <t>+0.85%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1055</v>
+        <v>236.5</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.30%33,000</t>
+          <t>0.29%135,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.29%</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>33000</v>
+        <v>135000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:38</t>
+          <t>2026-10-06 19:17:46</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,16 +3010,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+2.77%557</t>
+          <t>+3.95%579</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+2.77%</t>
+          <t>+3.95%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>557</v>
+        <v>579</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:38</t>
+          <t>2026-10-06 19:17:46</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,25 +3071,25 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-0.47%105.5</t>
+          <t>-0.95%104.5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-0.47%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>105.5</v>
+        <v>104.5</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.27%266,000</t>
+          <t>0.26%266,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.26%</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:38</t>
+          <t>2026-10-06 19:17:46</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+5.86%298</t>
+          <t>+0.34%299</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+5.86%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:38</t>
+          <t>2026-10-06 19:17:46</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,25 +3188,25 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>6147頎邦</t>
+          <t>2313華通</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-3.14%216</t>
+          <t>+1.41%252</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-3.14%</t>
+          <t>+1.41%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>216</v>
+        <v>252</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.25%113,000</t>
+          <t>0.25%110,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3215,11 +3215,11 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>113000</v>
+        <v>110000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:40</t>
+          <t>2026-10-06 19:17:47</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3249,38 +3249,38 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2313華通</t>
+          <t>6147頎邦</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+9.96%248.5</t>
+          <t>+0.23%216.5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+9.96%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>248.5</v>
+        <v>216.5</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.24%110,000</t>
+          <t>0.23%113,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>0.23%</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>110000</v>
+        <v>113000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:40</t>
+          <t>2026-10-06 19:17:47</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,25 +3315,25 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-0.31%47.9</t>
+          <t>-0.42%47.7</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>47.9</v>
+        <v>47.7</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.21%459,000</t>
+          <t>0.20%459,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:40</t>
+          <t>2026-10-06 19:17:47</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,25 +3376,25 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-1.06%41.9</t>
+          <t>-0.84%41.55</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-1.06%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>41.9</v>
+        <v>41.55</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.20%487,000</t>
+          <t>0.19%487,000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.19%</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:40</t>
+          <t>2026-10-06 19:17:47</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,25 +3437,25 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+0.24%2100</t>
+          <t>-0.48%2090</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>2100</v>
+        <v>2090</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.20%10,000</t>
+          <t>0.19%10,000</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.19%</t>
         </is>
       </c>
       <c r="K50" t="n">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:40</t>
+          <t>2026-10-06 19:17:47</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,25 +3498,25 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+9.76%1630</t>
+          <t>+5.21%1715</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+9.76%</t>
+          <t>+5.21%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1630</v>
+        <v>1715</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.16%11,000</t>
+          <t>0.17%11,000</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>0.17%</t>
         </is>
       </c>
       <c r="K51" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:40</t>
+          <t>2026-10-06 19:17:47</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3559,16 +3559,16 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>0%1295</t>
+          <t>-2.32%1265</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-2.32%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>1295</v>
+        <v>1265</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">

--- a/etf_holdings/2026-10-06_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00993A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:43</t>
+          <t>2026-10-06 23:28:48</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:43</t>
+          <t>2026-10-06 23:28:48</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:43</t>
+          <t>2026-10-06 23:28:48</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:43</t>
+          <t>2026-10-06 23:28:48</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:43</t>
+          <t>2026-10-06 23:28:48</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:43</t>
+          <t>2026-10-06 23:28:48</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:43</t>
+          <t>2026-10-06 23:28:48</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:43</t>
+          <t>2026-10-06 23:28:48</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:43</t>
+          <t>2026-10-06 23:28:48</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:43</t>
+          <t>2026-10-06 23:28:48</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:43</t>
+          <t>2026-10-06 23:28:48</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:43</t>
+          <t>2026-10-06 23:28:48</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:43</t>
+          <t>2026-10-06 23:28:48</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:43</t>
+          <t>2026-10-06 23:28:48</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:43</t>
+          <t>2026-10-06 23:28:48</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:44</t>
+          <t>2026-10-06 23:28:49</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:44</t>
+          <t>2026-10-06 23:28:49</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:44</t>
+          <t>2026-10-06 23:28:49</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:44</t>
+          <t>2026-10-06 23:28:49</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:44</t>
+          <t>2026-10-06 23:28:49</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:44</t>
+          <t>2026-10-06 23:28:49</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:44</t>
+          <t>2026-10-06 23:28:49</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:44</t>
+          <t>2026-10-06 23:28:49</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:44</t>
+          <t>2026-10-06 23:28:49</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:44</t>
+          <t>2026-10-06 23:28:49</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:44</t>
+          <t>2026-10-06 23:28:49</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:44</t>
+          <t>2026-10-06 23:28:49</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:44</t>
+          <t>2026-10-06 23:28:49</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:44</t>
+          <t>2026-10-06 23:28:49</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:44</t>
+          <t>2026-10-06 23:28:49</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:46</t>
+          <t>2026-10-06 23:28:50</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:46</t>
+          <t>2026-10-06 23:28:50</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:46</t>
+          <t>2026-10-06 23:28:50</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:46</t>
+          <t>2026-10-06 23:28:50</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:46</t>
+          <t>2026-10-06 23:28:50</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:46</t>
+          <t>2026-10-06 23:28:50</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:46</t>
+          <t>2026-10-06 23:28:50</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:46</t>
+          <t>2026-10-06 23:28:50</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:46</t>
+          <t>2026-10-06 23:28:50</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:46</t>
+          <t>2026-10-06 23:28:50</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:46</t>
+          <t>2026-10-06 23:28:50</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:46</t>
+          <t>2026-10-06 23:28:50</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:46</t>
+          <t>2026-10-06 23:28:50</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:46</t>
+          <t>2026-10-06 23:28:50</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:46</t>
+          <t>2026-10-06 23:28:50</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:47</t>
+          <t>2026-10-06 23:28:52</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:47</t>
+          <t>2026-10-06 23:28:52</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:47</t>
+          <t>2026-10-06 23:28:52</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:47</t>
+          <t>2026-10-06 23:28:52</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:47</t>
+          <t>2026-10-06 23:28:52</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:47</t>
+          <t>2026-10-06 23:28:52</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">

--- a/etf_holdings/2026-10-06_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00993A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:48</t>
+          <t>2026-10-06 23:59:23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:48</t>
+          <t>2026-10-06 23:59:23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:48</t>
+          <t>2026-10-06 23:59:23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:48</t>
+          <t>2026-10-06 23:59:23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:48</t>
+          <t>2026-10-06 23:59:23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:48</t>
+          <t>2026-10-06 23:59:23</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:48</t>
+          <t>2026-10-06 23:59:23</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:48</t>
+          <t>2026-10-06 23:59:23</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:48</t>
+          <t>2026-10-06 23:59:23</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:48</t>
+          <t>2026-10-06 23:59:23</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:48</t>
+          <t>2026-10-06 23:59:23</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:48</t>
+          <t>2026-10-06 23:59:23</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:48</t>
+          <t>2026-10-06 23:59:23</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:48</t>
+          <t>2026-10-06 23:59:23</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:48</t>
+          <t>2026-10-06 23:59:23</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:49</t>
+          <t>2026-10-06 23:59:24</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:49</t>
+          <t>2026-10-06 23:59:24</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:49</t>
+          <t>2026-10-06 23:59:24</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:49</t>
+          <t>2026-10-06 23:59:24</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:49</t>
+          <t>2026-10-06 23:59:24</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:49</t>
+          <t>2026-10-06 23:59:24</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:49</t>
+          <t>2026-10-06 23:59:24</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:49</t>
+          <t>2026-10-06 23:59:24</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:49</t>
+          <t>2026-10-06 23:59:24</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:49</t>
+          <t>2026-10-06 23:59:24</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:49</t>
+          <t>2026-10-06 23:59:24</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:49</t>
+          <t>2026-10-06 23:59:24</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:49</t>
+          <t>2026-10-06 23:59:24</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:49</t>
+          <t>2026-10-06 23:59:24</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:49</t>
+          <t>2026-10-06 23:59:24</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:50</t>
+          <t>2026-10-06 23:59:26</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:50</t>
+          <t>2026-10-06 23:59:26</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:50</t>
+          <t>2026-10-06 23:59:26</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:50</t>
+          <t>2026-10-06 23:59:26</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:50</t>
+          <t>2026-10-06 23:59:26</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:50</t>
+          <t>2026-10-06 23:59:26</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:50</t>
+          <t>2026-10-06 23:59:26</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:50</t>
+          <t>2026-10-06 23:59:26</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:50</t>
+          <t>2026-10-06 23:59:26</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:50</t>
+          <t>2026-10-06 23:59:26</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:50</t>
+          <t>2026-10-06 23:59:26</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:50</t>
+          <t>2026-10-06 23:59:26</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:50</t>
+          <t>2026-10-06 23:59:26</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:50</t>
+          <t>2026-10-06 23:59:26</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:50</t>
+          <t>2026-10-06 23:59:26</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:52</t>
+          <t>2026-10-06 23:59:27</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:52</t>
+          <t>2026-10-06 23:59:27</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:52</t>
+          <t>2026-10-06 23:59:27</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:52</t>
+          <t>2026-10-06 23:59:27</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:52</t>
+          <t>2026-10-06 23:59:27</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:52</t>
+          <t>2026-10-06 23:59:27</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
